--- a/Lenguaje/SpeUse.xlsx
+++ b/Lenguaje/SpeUse.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upvedues-my.sharepoint.com/personal/zyyeche_upv_edu_es/Documents/Thalassar/Colangs/Lenguaje/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="274" documentId="11_AD4D2F04E46CFB4ACB3E20196D56F008693EDF13" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07A388E9-374F-4895-8272-67F73F8AB205}"/>
+  <xr:revisionPtr revIDLastSave="345" documentId="11_AD4D2F04E46CFB4ACB3E20196D56F008693EDF13" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C72AC27-21F1-46DE-A49F-19CEBECCF041}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="990" yWindow="3165" windowWidth="16230" windowHeight="9450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="130">
   <si>
     <t>灵灰</t>
   </si>
@@ -482,6 +482,22 @@
   </si>
   <si>
     <t>不可数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gender</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Das</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Die</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Der</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -689,7 +705,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -733,7 +749,161 @@
     <cellStyle name="Encabezado 1" xfId="1" builtinId="16"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="55">
+  <dxfs count="66">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -1516,135 +1686,150 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{15694CC2-0839-46DE-9306-71DF7D18EC8A}" name="Tabla2" displayName="Tabla2" ref="F5:H12" totalsRowShown="0" headerRowDxfId="54" dataDxfId="50">
-  <autoFilter ref="F5:H12" xr:uid="{15694CC2-0839-46DE-9306-71DF7D18EC8A}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{7BF31AAA-F7BA-49C4-B837-B7A63E3E176F}" name="国家名" dataDxfId="53">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{15694CC2-0839-46DE-9306-71DF7D18EC8A}" name="Tabla2" displayName="Tabla2" ref="F5:I12" totalsRowShown="0" headerRowDxfId="65" dataDxfId="64">
+  <autoFilter ref="F5:I12" xr:uid="{15694CC2-0839-46DE-9306-71DF7D18EC8A}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{7BF31AAA-F7BA-49C4-B837-B7A63E3E176F}" name="国家名" dataDxfId="63">
       <calculatedColumnFormula>A3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3EE510B2-9EEE-4D68-A98F-37A7371F9B12}" name="Cr" dataDxfId="52"/>
-    <tableColumn id="3" xr3:uid="{B1738400-453F-40A6-89AC-31EC265201D7}" name="他称" dataDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{3EE510B2-9EEE-4D68-A98F-37A7371F9B12}" name="Cr" dataDxfId="62"/>
+    <tableColumn id="3" xr3:uid="{B1738400-453F-40A6-89AC-31EC265201D7}" name="他称" dataDxfId="61"/>
+    <tableColumn id="4" xr3:uid="{21197381-6376-4490-A892-94C806847FC7}" name="Gender" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{4656DEF4-F077-4C52-A041-7F580B7082C9}" name="Tabla3512" displayName="Tabla3512" ref="F68:H72" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="F68:H72" xr:uid="{4656DEF4-F077-4C52-A041-7F580B7082C9}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{88745775-4E04-4761-9CFD-F40C07CD5BB9}" name="矿物" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{8F0158BA-65D8-406F-AB5A-97F5CC1B30F3}" name="Cr" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{36D6C69E-DA27-417D-977D-28670DE08B72}" name="复数" dataDxfId="7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{4656DEF4-F077-4C52-A041-7F580B7082C9}" name="Tabla3512" displayName="Tabla3512" ref="F68:I72" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+  <autoFilter ref="F68:I72" xr:uid="{4656DEF4-F077-4C52-A041-7F580B7082C9}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{88745775-4E04-4761-9CFD-F40C07CD5BB9}" name="矿物" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{8F0158BA-65D8-406F-AB5A-97F5CC1B30F3}" name="Cr" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{36D6C69E-DA27-417D-977D-28670DE08B72}" name="复数" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{3121F5B9-B016-4FC2-91BA-93BB6613E308}" name="Gender" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{71705A75-E7AA-44A5-9C69-185EE5F16B96}" name="Tabla351013" displayName="Tabla351013" ref="F56:H60" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
-  <autoFilter ref="F56:H60" xr:uid="{71705A75-E7AA-44A5-9C69-185EE5F16B96}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{8233C6FA-3FBD-4AC1-8771-A3702745E59B}" name="矿物" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{9DB61B1E-DEDD-42DC-96EF-9B5AF69BD512}" name="Cr" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{B28F4E6C-66E3-48D2-BDCF-13404E65E356}" name="复数" dataDxfId="2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{71705A75-E7AA-44A5-9C69-185EE5F16B96}" name="Tabla351013" displayName="Tabla351013" ref="F56:I60" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+  <autoFilter ref="F56:I60" xr:uid="{71705A75-E7AA-44A5-9C69-185EE5F16B96}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{8233C6FA-3FBD-4AC1-8771-A3702745E59B}" name="矿物" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{9DB61B1E-DEDD-42DC-96EF-9B5AF69BD512}" name="Cr" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{B28F4E6C-66E3-48D2-BDCF-13404E65E356}" name="复数" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{6D71638D-B27D-4D59-888C-375C497BD207}" name="Gender" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{EDD2FE4E-8319-476A-ADDE-0BDDB6F682FA}" name="Tabla3" displayName="Tabla3" ref="F15:H18" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
-  <autoFilter ref="F15:H18" xr:uid="{EDD2FE4E-8319-476A-ADDE-0BDDB6F682FA}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{AF5C0C5A-37B4-4392-9B15-E2BFFBC13E81}" name="矿物" dataDxfId="49"/>
-    <tableColumn id="2" xr3:uid="{A9ABF68E-0561-41B6-9239-6B3FD7A57077}" name="Cr" dataDxfId="48"/>
-    <tableColumn id="3" xr3:uid="{23B55245-21F5-4186-A52A-1A0F80AFA99F}" name="复数" dataDxfId="47"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{EDD2FE4E-8319-476A-ADDE-0BDDB6F682FA}" name="Tabla3" displayName="Tabla3" ref="F15:I18" totalsRowShown="0" headerRowDxfId="60" dataDxfId="59">
+  <autoFilter ref="F15:I18" xr:uid="{EDD2FE4E-8319-476A-ADDE-0BDDB6F682FA}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{AF5C0C5A-37B4-4392-9B15-E2BFFBC13E81}" name="矿物" dataDxfId="58"/>
+    <tableColumn id="2" xr3:uid="{A9ABF68E-0561-41B6-9239-6B3FD7A57077}" name="Cr" dataDxfId="57"/>
+    <tableColumn id="3" xr3:uid="{23B55245-21F5-4186-A52A-1A0F80AFA99F}" name="复数" dataDxfId="56"/>
+    <tableColumn id="4" xr3:uid="{4034C858-85C4-4628-BAD0-2822D3E6AC62}" name="Gender" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2D60BA0E-C90D-462B-BC0F-BE69C3C1395C}" name="Tabla35" displayName="Tabla35" ref="F20:H24" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40">
-  <autoFilter ref="F20:H24" xr:uid="{2D60BA0E-C90D-462B-BC0F-BE69C3C1395C}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{50285B20-3BFD-4292-BB67-879C558DEF2B}" name="矿物" dataDxfId="44"/>
-    <tableColumn id="2" xr3:uid="{C8114876-675C-4926-96B8-30B5D3D43EE3}" name="Cr" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{E6465656-8149-4618-BD92-33E600C3ADCE}" name="复数" dataDxfId="42"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2D60BA0E-C90D-462B-BC0F-BE69C3C1395C}" name="Tabla35" displayName="Tabla35" ref="F20:I24" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
+  <autoFilter ref="F20:I24" xr:uid="{2D60BA0E-C90D-462B-BC0F-BE69C3C1395C}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{50285B20-3BFD-4292-BB67-879C558DEF2B}" name="矿物" dataDxfId="53"/>
+    <tableColumn id="2" xr3:uid="{C8114876-675C-4926-96B8-30B5D3D43EE3}" name="Cr" dataDxfId="52"/>
+    <tableColumn id="3" xr3:uid="{E6465656-8149-4618-BD92-33E600C3ADCE}" name="复数" dataDxfId="51"/>
+    <tableColumn id="4" xr3:uid="{33699D8B-473F-4159-A73A-EC05EC85FCD2}" name="Gender" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{701FF396-56A6-47FB-854F-6265BDF57063}" name="Tabla36" displayName="Tabla36" ref="F26:H29" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
-  <autoFilter ref="F26:H29" xr:uid="{701FF396-56A6-47FB-854F-6265BDF57063}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{EE8FA4C8-189C-4875-9360-CC2C17ADF0B7}" name="矿物" dataDxfId="39"/>
-    <tableColumn id="2" xr3:uid="{90EB7737-26F1-436B-A4D0-BE700241FC5D}" name="Cr" dataDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{E5373B55-E4EA-4EEB-9776-9DFE1CA59D26}" name="复数" dataDxfId="37"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{701FF396-56A6-47FB-854F-6265BDF57063}" name="Tabla36" displayName="Tabla36" ref="F26:I29" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49">
+  <autoFilter ref="F26:I29" xr:uid="{701FF396-56A6-47FB-854F-6265BDF57063}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{EE8FA4C8-189C-4875-9360-CC2C17ADF0B7}" name="矿物" dataDxfId="48"/>
+    <tableColumn id="2" xr3:uid="{90EB7737-26F1-436B-A4D0-BE700241FC5D}" name="Cr" dataDxfId="47"/>
+    <tableColumn id="3" xr3:uid="{E5373B55-E4EA-4EEB-9776-9DFE1CA59D26}" name="复数" dataDxfId="46"/>
+    <tableColumn id="4" xr3:uid="{2EAF8A47-CED0-4F00-99BC-4C6BC619F98D}" name="Gender" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{7A174662-182D-459E-BF9B-3CB6AC780B1E}" name="Tabla37" displayName="Tabla37" ref="F31:H37" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
-  <autoFilter ref="F31:H37" xr:uid="{7A174662-182D-459E-BF9B-3CB6AC780B1E}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{5F069A24-42DE-4B38-9728-F986A69B1C05}" name="矿物" dataDxfId="34"/>
-    <tableColumn id="2" xr3:uid="{DAE8458C-188D-4702-826E-D77594D583E0}" name="Cr" dataDxfId="33"/>
-    <tableColumn id="3" xr3:uid="{EE87D088-369E-4417-93EF-E44909DB57AA}" name="复数" dataDxfId="32"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{7A174662-182D-459E-BF9B-3CB6AC780B1E}" name="Tabla37" displayName="Tabla37" ref="F31:I37" totalsRowShown="0" headerRowDxfId="45" dataDxfId="44">
+  <autoFilter ref="F31:I37" xr:uid="{7A174662-182D-459E-BF9B-3CB6AC780B1E}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{5F069A24-42DE-4B38-9728-F986A69B1C05}" name="矿物" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{DAE8458C-188D-4702-826E-D77594D583E0}" name="Cr" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{EE87D088-369E-4417-93EF-E44909DB57AA}" name="复数" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{3C1A7F9E-2CEA-4548-BB0C-05E83E1A654E}" name="Gender" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{31BB3A3F-5B46-47F1-A7CF-F5D1A4CEA07C}" name="Tabla38" displayName="Tabla38" ref="F39:H43" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
-  <autoFilter ref="F39:H43" xr:uid="{31BB3A3F-5B46-47F1-A7CF-F5D1A4CEA07C}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{2762A289-4B82-45C5-9708-A8B9AC19A4A5}" name="矿物" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{2C624EB1-5440-4E03-B3D3-D9042FA31B67}" name="Cr" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{F27769C6-E45F-42BB-90AB-F905AF01C735}" name="复数" dataDxfId="27"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{31BB3A3F-5B46-47F1-A7CF-F5D1A4CEA07C}" name="Tabla38" displayName="Tabla38" ref="F39:I43" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
+  <autoFilter ref="F39:I43" xr:uid="{31BB3A3F-5B46-47F1-A7CF-F5D1A4CEA07C}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{2762A289-4B82-45C5-9708-A8B9AC19A4A5}" name="矿物" dataDxfId="38"/>
+    <tableColumn id="2" xr3:uid="{2C624EB1-5440-4E03-B3D3-D9042FA31B67}" name="Cr" dataDxfId="37"/>
+    <tableColumn id="3" xr3:uid="{F27769C6-E45F-42BB-90AB-F905AF01C735}" name="复数" dataDxfId="36"/>
+    <tableColumn id="4" xr3:uid="{E03755B3-8905-4C19-872A-C4393BCFEEAE}" name="Gender" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{49A7B1E1-8EA6-4D71-8E04-611BBFEA0AE8}" name="Tabla39" displayName="Tabla39" ref="F45:H48" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
-  <autoFilter ref="F45:H48" xr:uid="{49A7B1E1-8EA6-4D71-8E04-611BBFEA0AE8}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{9A613D6A-3151-493C-8D20-9F195BF2A0EB}" name="矿物" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{BCF0AF72-AE8F-47B3-BA5B-0442157D6E7F}" name="Cr" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{DC54D233-1277-40C0-B7C2-9CDA9C2309A4}" name="复数" dataDxfId="22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{49A7B1E1-8EA6-4D71-8E04-611BBFEA0AE8}" name="Tabla39" displayName="Tabla39" ref="F45:I48" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34">
+  <autoFilter ref="F45:I48" xr:uid="{49A7B1E1-8EA6-4D71-8E04-611BBFEA0AE8}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{9A613D6A-3151-493C-8D20-9F195BF2A0EB}" name="矿物" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{BCF0AF72-AE8F-47B3-BA5B-0442157D6E7F}" name="Cr" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{DC54D233-1277-40C0-B7C2-9CDA9C2309A4}" name="复数" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{D187AEFA-3A01-4DF6-98D9-BE65E3E76BEB}" name="Gender" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{8DD01002-C9CE-4211-9684-4261145AA94D}" name="Tabla3510" displayName="Tabla3510" ref="F50:H54" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="F50:H54" xr:uid="{8DD01002-C9CE-4211-9684-4261145AA94D}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{1D3D58B9-007A-4800-AAF7-A11584DB3C84}" name="矿物" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{0F86BE51-F937-494F-8BCD-B1EBE8F3AEDB}" name="Cr" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{5EAD5E0A-7713-4CF8-8368-77BB66AEEC0F}" name="复数" dataDxfId="17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{8DD01002-C9CE-4211-9684-4261145AA94D}" name="Tabla3510" displayName="Tabla3510" ref="F50:I54" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+  <autoFilter ref="F50:I54" xr:uid="{8DD01002-C9CE-4211-9684-4261145AA94D}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{1D3D58B9-007A-4800-AAF7-A11584DB3C84}" name="矿物" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{0F86BE51-F937-494F-8BCD-B1EBE8F3AEDB}" name="Cr" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{5EAD5E0A-7713-4CF8-8368-77BB66AEEC0F}" name="复数" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{E8EC5606-9FDA-446A-AE77-8AFA346468CA}" name="Gender" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{5D055E8B-C98E-4A05-8BAA-3AC1CD9EC625}" name="Tabla3511" displayName="Tabla3511" ref="F62:H66" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="F62:H66" xr:uid="{5D055E8B-C98E-4A05-8BAA-3AC1CD9EC625}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{04C3D206-A9B9-4865-BF1F-E0B29F7970F6}" name="矿物" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{CAEAEAB7-1402-4E74-936D-B67A4C0A9E27}" name="Cr" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{34066718-6C70-4485-B496-70243A21F1CC}" name="复数" dataDxfId="12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{5D055E8B-C98E-4A05-8BAA-3AC1CD9EC625}" name="Tabla3511" displayName="Tabla3511" ref="F62:I66" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
+  <autoFilter ref="F62:I66" xr:uid="{5D055E8B-C98E-4A05-8BAA-3AC1CD9EC625}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{04C3D206-A9B9-4865-BF1F-E0B29F7970F6}" name="矿物" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{CAEAEAB7-1402-4E74-936D-B67A4C0A9E27}" name="Cr" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{34066718-6C70-4485-B496-70243A21F1CC}" name="复数" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{113D54F1-56AF-4C56-A668-4CFEBF9D01C4}" name="Gender" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1924,7 +2109,7 @@
     <col min="6" max="6" width="14.25" customWidth="1"/>
     <col min="7" max="7" width="16.375" customWidth="1"/>
     <col min="8" max="8" width="17.5" customWidth="1"/>
-    <col min="9" max="9" width="3.5" customWidth="1"/>
+    <col min="9" max="9" width="16.625" customWidth="1"/>
     <col min="10" max="10" width="34" customWidth="1"/>
     <col min="11" max="11" width="3" customWidth="1"/>
   </cols>
@@ -1974,6 +2159,9 @@
       <c r="H5" s="13" t="s">
         <v>68</v>
       </c>
+      <c r="I5" s="13" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="6" spans="1:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
@@ -1988,6 +2176,9 @@
       <c r="H6" s="13" t="s">
         <v>67</v>
       </c>
+      <c r="I6" s="13" t="s">
+        <v>127</v>
+      </c>
       <c r="J6" s="20" t="s">
         <v>82</v>
       </c>
@@ -1997,7 +2188,7 @@
         <v>6</v>
       </c>
       <c r="F7" s="13" t="str">
-        <f>A5</f>
+        <f t="shared" ref="F7:F12" si="0">A5</f>
         <v>塞尔瑞</v>
       </c>
       <c r="G7" s="18" t="s">
@@ -2005,6 +2196,9 @@
       </c>
       <c r="H7" s="13" t="s">
         <v>70</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>127</v>
       </c>
       <c r="J7" s="12" t="s">
         <v>96</v>
@@ -2015,7 +2209,7 @@
         <v>7</v>
       </c>
       <c r="F8" s="13" t="str">
-        <f>A6</f>
+        <f t="shared" si="0"/>
         <v>埃多拉</v>
       </c>
       <c r="G8" s="19" t="s">
@@ -2023,6 +2217,9 @@
       </c>
       <c r="H8" s="13" t="s">
         <v>72</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2030,7 +2227,7 @@
         <v>8</v>
       </c>
       <c r="F9" s="13" t="str">
-        <f>A7</f>
+        <f t="shared" si="0"/>
         <v>斯彼伯龙</v>
       </c>
       <c r="G9" s="19" t="s">
@@ -2038,6 +2235,9 @@
       </c>
       <c r="H9" s="13" t="s">
         <v>74</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2045,7 +2245,7 @@
         <v>9</v>
       </c>
       <c r="F10" s="13" t="str">
-        <f>A8</f>
+        <f t="shared" si="0"/>
         <v>威尔迪亚</v>
       </c>
       <c r="G10" s="19" t="s">
@@ -2053,6 +2253,9 @@
       </c>
       <c r="H10" s="13" t="s">
         <v>76</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2060,7 +2263,7 @@
         <v>10</v>
       </c>
       <c r="F11" s="13" t="str">
-        <f>A9</f>
+        <f t="shared" si="0"/>
         <v>萨尔穆拉</v>
       </c>
       <c r="G11" s="19" t="s">
@@ -2068,6 +2271,9 @@
       </c>
       <c r="H11" s="13" t="s">
         <v>78</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2075,7 +2281,7 @@
         <v>11</v>
       </c>
       <c r="F12" s="13" t="str">
-        <f>A10</f>
+        <f t="shared" si="0"/>
         <v>蒙希因</v>
       </c>
       <c r="G12" s="19" t="s">
@@ -2083,6 +2289,9 @@
       </c>
       <c r="H12" s="13" t="s">
         <v>80</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -2108,6 +2317,9 @@
       <c r="H15" s="23" t="s">
         <v>107</v>
       </c>
+      <c r="I15" s="12" t="s">
+        <v>126</v>
+      </c>
       <c r="J15" s="20" t="s">
         <v>115</v>
       </c>
@@ -2125,6 +2337,9 @@
       <c r="H16" s="23" t="s">
         <v>108</v>
       </c>
+      <c r="I16" s="12" t="s">
+        <v>128</v>
+      </c>
       <c r="J16" s="22" t="s">
         <v>116</v>
       </c>
@@ -2138,6 +2353,9 @@
       </c>
       <c r="G17" s="23"/>
       <c r="H17" s="23"/>
+      <c r="I17" s="12" t="s">
+        <v>128</v>
+      </c>
       <c r="J17" s="11" t="s">
         <v>117</v>
       </c>
@@ -2151,6 +2369,9 @@
       </c>
       <c r="G18" s="12"/>
       <c r="H18" s="23"/>
+      <c r="I18" s="12" t="s">
+        <v>128</v>
+      </c>
       <c r="J18" s="11" t="s">
         <v>118</v>
       </c>
@@ -2179,6 +2400,9 @@
       <c r="H20" s="23" t="s">
         <v>107</v>
       </c>
+      <c r="I20" s="12" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="21" spans="1:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
@@ -2193,6 +2417,9 @@
       <c r="H21" s="23" t="s">
         <v>109</v>
       </c>
+      <c r="I21" s="12" t="s">
+        <v>129</v>
+      </c>
       <c r="J21" s="20" t="s">
         <v>124</v>
       </c>
@@ -2206,6 +2433,9 @@
       </c>
       <c r="G22" s="23"/>
       <c r="H22" s="23"/>
+      <c r="I22" s="12" t="s">
+        <v>129</v>
+      </c>
       <c r="J22" s="22" t="s">
         <v>120</v>
       </c>
@@ -2219,6 +2449,9 @@
       </c>
       <c r="G23" s="23"/>
       <c r="H23" s="23"/>
+      <c r="I23" s="12" t="s">
+        <v>129</v>
+      </c>
       <c r="J23" s="11" t="s">
         <v>121</v>
       </c>
@@ -2232,6 +2465,9 @@
       </c>
       <c r="G24" s="23"/>
       <c r="H24" s="23"/>
+      <c r="I24" s="12" t="s">
+        <v>129</v>
+      </c>
       <c r="J24" s="11" t="s">
         <v>122</v>
       </c>
@@ -2260,6 +2496,9 @@
       <c r="H26" s="23" t="s">
         <v>107</v>
       </c>
+      <c r="I26" s="12" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="27" spans="1:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
@@ -2274,6 +2513,9 @@
       <c r="H27" s="23" t="s">
         <v>110</v>
       </c>
+      <c r="I27" s="12" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="28" spans="1:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
@@ -2284,6 +2526,9 @@
       </c>
       <c r="G28" s="23"/>
       <c r="H28" s="23"/>
+      <c r="I28" s="12" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="29" spans="1:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
@@ -2294,6 +2539,9 @@
       </c>
       <c r="G29" s="23"/>
       <c r="H29" s="23"/>
+      <c r="I29" s="12" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="30" spans="1:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
@@ -2316,6 +2564,9 @@
       <c r="H31" s="23" t="s">
         <v>107</v>
       </c>
+      <c r="I31" s="12" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="32" spans="1:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
@@ -2330,8 +2581,11 @@
       <c r="H32" s="23" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I32" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>31</v>
       </c>
@@ -2340,8 +2594,11 @@
       </c>
       <c r="G33" s="23"/>
       <c r="H33" s="23"/>
-    </row>
-    <row r="34" spans="1:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I33" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>32</v>
       </c>
@@ -2350,8 +2607,11 @@
       </c>
       <c r="G34" s="23"/>
       <c r="H34" s="23"/>
-    </row>
-    <row r="35" spans="1:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I34" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>33</v>
       </c>
@@ -2360,8 +2620,11 @@
       </c>
       <c r="G35" s="23"/>
       <c r="H35" s="23"/>
-    </row>
-    <row r="36" spans="1:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I35" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>34</v>
       </c>
@@ -2370,8 +2633,11 @@
       </c>
       <c r="G36" s="23"/>
       <c r="H36" s="23"/>
-    </row>
-    <row r="37" spans="1:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I36" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>35</v>
       </c>
@@ -2380,8 +2646,11 @@
       </c>
       <c r="G37" s="23"/>
       <c r="H37" s="23"/>
-    </row>
-    <row r="38" spans="1:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I37" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>36</v>
       </c>
@@ -2389,7 +2658,7 @@
       <c r="G38" s="23"/>
       <c r="H38" s="23"/>
     </row>
-    <row r="39" spans="1:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>37</v>
       </c>
@@ -2402,8 +2671,11 @@
       <c r="H39" s="23" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I39" s="12" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>38</v>
       </c>
@@ -2416,8 +2688,11 @@
       <c r="H40" s="23" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I40" s="12" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>39</v>
       </c>
@@ -2426,8 +2701,11 @@
       </c>
       <c r="G41" s="23"/>
       <c r="H41" s="23"/>
-    </row>
-    <row r="42" spans="1:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I41" s="12" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>40</v>
       </c>
@@ -2436,8 +2714,11 @@
       </c>
       <c r="G42" s="23"/>
       <c r="H42" s="23"/>
-    </row>
-    <row r="43" spans="1:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I42" s="12" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>41</v>
       </c>
@@ -2446,8 +2727,11 @@
       </c>
       <c r="G43" s="23"/>
       <c r="H43" s="23"/>
-    </row>
-    <row r="44" spans="1:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I43" s="12" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>42</v>
       </c>
@@ -2455,7 +2739,7 @@
       <c r="G44" s="23"/>
       <c r="H44" s="23"/>
     </row>
-    <row r="45" spans="1:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>43</v>
       </c>
@@ -2468,8 +2752,11 @@
       <c r="H45" s="23" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I45" s="12" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>44</v>
       </c>
@@ -2482,8 +2769,11 @@
       <c r="H46" s="23" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I46" s="12" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>45</v>
       </c>
@@ -2492,8 +2782,11 @@
       </c>
       <c r="G47" s="23"/>
       <c r="H47" s="23"/>
-    </row>
-    <row r="48" spans="1:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I47" s="12" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>46</v>
       </c>
@@ -2502,6 +2795,9 @@
       </c>
       <c r="G48" s="23"/>
       <c r="H48" s="23"/>
+      <c r="I48" s="12" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="49" spans="1:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
@@ -2524,6 +2820,9 @@
       <c r="H50" s="23" t="s">
         <v>107</v>
       </c>
+      <c r="I50" s="12" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="51" spans="1:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
@@ -2538,6 +2837,9 @@
       <c r="H51" s="23" t="s">
         <v>113</v>
       </c>
+      <c r="I51" s="12" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="52" spans="1:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
@@ -2548,6 +2850,9 @@
       </c>
       <c r="G52" s="23"/>
       <c r="H52" s="23"/>
+      <c r="I52" s="12" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="53" spans="1:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
@@ -2558,6 +2863,9 @@
       </c>
       <c r="G53" s="23"/>
       <c r="H53" s="23"/>
+      <c r="I53" s="12" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="54" spans="1:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
@@ -2568,6 +2876,9 @@
       </c>
       <c r="G54" s="23"/>
       <c r="H54" s="23"/>
+      <c r="I54" s="12" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="55" spans="1:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
@@ -2590,6 +2901,9 @@
       <c r="H56" s="23" t="s">
         <v>107</v>
       </c>
+      <c r="I56" s="12" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="57" spans="1:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
@@ -2604,6 +2918,9 @@
       <c r="H57" s="23" t="s">
         <v>103</v>
       </c>
+      <c r="I57" s="12" t="s">
+        <v>128</v>
+      </c>
       <c r="J57" t="s">
         <v>125</v>
       </c>
@@ -2617,6 +2934,9 @@
       </c>
       <c r="G58" s="23"/>
       <c r="H58" s="23"/>
+      <c r="I58" s="12" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="59" spans="1:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
@@ -2627,6 +2947,9 @@
       </c>
       <c r="G59" s="23"/>
       <c r="H59" s="23"/>
+      <c r="I59" s="12" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="60" spans="1:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
@@ -2637,6 +2960,9 @@
       </c>
       <c r="G60" s="23"/>
       <c r="H60" s="23"/>
+      <c r="I60" s="12" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="61" spans="1:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
@@ -2656,6 +2982,9 @@
       <c r="H62" s="23" t="s">
         <v>107</v>
       </c>
+      <c r="I62" s="12" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="F63" s="23" t="s">
@@ -2667,6 +2996,9 @@
       <c r="H63" s="23" t="s">
         <v>105</v>
       </c>
+      <c r="I63" s="12" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="F64" s="23" t="s">
@@ -2674,27 +3006,36 @@
       </c>
       <c r="G64" s="23"/>
       <c r="H64" s="23"/>
-    </row>
-    <row r="65" spans="6:8" x14ac:dyDescent="0.35">
+      <c r="I64" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="65" spans="6:9" x14ac:dyDescent="0.35">
       <c r="F65" s="23" t="s">
         <v>52</v>
       </c>
       <c r="G65" s="23"/>
       <c r="H65" s="23"/>
-    </row>
-    <row r="66" spans="6:8" x14ac:dyDescent="0.35">
+      <c r="I65" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="66" spans="6:9" x14ac:dyDescent="0.35">
       <c r="F66" s="23" t="s">
         <v>53</v>
       </c>
       <c r="G66" s="23"/>
       <c r="H66" s="23"/>
-    </row>
-    <row r="67" spans="6:8" x14ac:dyDescent="0.35">
+      <c r="I66" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="67" spans="6:9" x14ac:dyDescent="0.35">
       <c r="F67" s="23"/>
       <c r="G67" s="23"/>
       <c r="H67" s="23"/>
     </row>
-    <row r="68" spans="6:8" x14ac:dyDescent="0.35">
+    <row r="68" spans="6:9" x14ac:dyDescent="0.35">
       <c r="F68" s="23" t="s">
         <v>83</v>
       </c>
@@ -2704,8 +3045,11 @@
       <c r="H68" s="23" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="69" spans="6:8" x14ac:dyDescent="0.35">
+      <c r="I68" s="12" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="69" spans="6:9" x14ac:dyDescent="0.35">
       <c r="F69" s="23" t="s">
         <v>94</v>
       </c>
@@ -2715,27 +3059,39 @@
       <c r="H69" s="23" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="70" spans="6:8" x14ac:dyDescent="0.35">
+      <c r="I69" s="12" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="70" spans="6:9" x14ac:dyDescent="0.35">
       <c r="F70" s="23" t="s">
         <v>57</v>
       </c>
       <c r="G70" s="23"/>
       <c r="H70" s="23"/>
-    </row>
-    <row r="71" spans="6:8" x14ac:dyDescent="0.35">
+      <c r="I70" s="12" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="71" spans="6:9" x14ac:dyDescent="0.35">
       <c r="F71" s="23" t="s">
         <v>58</v>
       </c>
       <c r="G71" s="23"/>
       <c r="H71" s="23"/>
-    </row>
-    <row r="72" spans="6:8" x14ac:dyDescent="0.35">
+      <c r="I71" s="12" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="72" spans="6:9" x14ac:dyDescent="0.35">
       <c r="F72" s="23" t="s">
         <v>59</v>
       </c>
       <c r="G72" s="23"/>
       <c r="H72" s="23"/>
+      <c r="I72" s="12" t="s">
+        <v>129</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
